--- a/People classification.xlsx
+++ b/People classification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/fabio-correa_cordeiro_capgemini_com/Documents/Documents/GitHub/Indigenous-Slavery-KG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FA302B3-CEAD-46B5-BAFF-4445213BE191}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBA5C56B-3630-4E9B-A274-43AF753AAFF0}"/>
   <bookViews>
-    <workbookView xWindow="-9420" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
+    <workbookView xWindow="-4620" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="101">
   <si>
     <t>tag:stardog:api:deus'</t>
   </si>
@@ -282,6 +282,63 @@
   </si>
   <si>
     <t xml:space="preserve"> 'tag:stardog:api:immanuel_kant'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:roger_bastide'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:nossa_senhora'</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:policia</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:ensino_medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag:stardog:api:es_sa	</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:seduc</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:tamb_em</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:candido_rondon'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:nossa_senhora_do_rosario'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag:stardog:api:festa	</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:letras</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:memorias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag:stardog:api:kariri	</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:friedrich_nietzsche'</t>
+  </si>
+  <si>
+    <t>tag:stardog:api:i_sso</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:bell_hooks'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:marques_de_pombal'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:hanna_arendt'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:carolina_maria_de_jesus'</t>
   </si>
 </sst>
 </file>
@@ -684,14 +741,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093B7361-491F-4850-B66C-DAB516A37F60}">
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
     <col min="2" max="2" width="32.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" style="2"/>
-    <col min="7" max="7" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="2"/>
+    <col min="7" max="7" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="17" width="11.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -752,8 +809,6 @@
       <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -763,7 +818,6 @@
       <c r="C4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
         <v>55</v>
       </c>
@@ -782,8 +836,6 @@
       <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
         <v>55</v>
@@ -802,8 +854,6 @@
       <c r="C6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -811,7 +861,9 @@
       <c r="K6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -820,8 +872,6 @@
       <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="V7" s="5"/>
     </row>
@@ -832,8 +882,6 @@
       <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="J8" s="2" t="s">
         <v>55</v>
@@ -849,7 +897,6 @@
       <c r="B9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
         <v>55</v>
       </c>
@@ -865,8 +912,6 @@
       <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
         <v>55</v>
@@ -885,8 +930,6 @@
       <c r="B11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -896,8 +939,6 @@
       <c r="C12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
         <v>55</v>
@@ -916,8 +957,6 @@
       <c r="C13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="J13" s="2" t="s">
         <v>55</v>
@@ -939,7 +978,6 @@
       <c r="F14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
         <v>55</v>
@@ -961,7 +999,6 @@
       <c r="F15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
         <v>55</v>
@@ -983,8 +1020,6 @@
       <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
         <v>55</v>
@@ -1006,8 +1041,6 @@
       <c r="D17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="J17" s="2" t="s">
         <v>55</v>
@@ -1015,7 +1048,9 @@
       <c r="K17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V17" s="5"/>
+      <c r="V17" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1027,13 +1062,15 @@
       <c r="F18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="J18" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
@@ -1043,9 +1080,10 @@
       <c r="B19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
+      <c r="V19" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1054,14 +1092,15 @@
       <c r="E20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="K20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
@@ -1071,7 +1110,6 @@
       <c r="C21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
         <v>55</v>
       </c>
@@ -1090,8 +1128,6 @@
       <c r="D22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="J22" s="2" t="s">
         <v>55</v>
@@ -1110,8 +1146,6 @@
       <c r="E23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
         <v>55</v>
@@ -1133,8 +1167,6 @@
       <c r="C24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="K24" s="2" t="s">
         <v>55</v>
@@ -1153,7 +1185,6 @@
       <c r="D25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
         <v>55</v>
       </c>
@@ -1164,13 +1195,14 @@
       <c r="L25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V25" s="5"/>
+      <c r="V25" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
         <v>55</v>
       </c>
@@ -1178,7 +1210,9 @@
       <c r="N26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V26" s="5"/>
+      <c r="V26" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1187,8 +1221,6 @@
       <c r="D27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="K27" s="2" t="s">
         <v>55</v>
@@ -1205,8 +1237,6 @@
       <c r="D28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="J28" s="2" t="s">
         <v>55</v>
@@ -1226,8 +1256,6 @@
       <c r="E29" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="L29" s="2" t="s">
         <v>55</v>
@@ -1250,7 +1278,6 @@
       <c r="F30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
         <v>55</v>
@@ -1270,8 +1297,6 @@
       <c r="B31" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="V31" s="5"/>
     </row>
@@ -1285,8 +1310,6 @@
       <c r="D32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
         <v>55</v>
@@ -1312,7 +1335,6 @@
       <c r="F33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
         <v>55</v>
@@ -1331,8 +1353,6 @@
       <c r="E34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="J34" s="2" t="s">
         <v>55</v>
@@ -1348,8 +1368,6 @@
       <c r="C35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
         <v>55</v>
@@ -1368,8 +1386,6 @@
       <c r="C36" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="L36" s="2" t="s">
         <v>55</v>
@@ -1388,8 +1404,6 @@
       <c r="E37" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="K37" s="2" t="s">
         <v>55</v>
@@ -1408,8 +1422,6 @@
       <c r="C38" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
         <v>55</v>
@@ -1420,7 +1432,9 @@
       <c r="K38" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V38" s="5"/>
+      <c r="V38" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -1429,14 +1443,15 @@
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="V39" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
@@ -1446,9 +1461,10 @@
       <c r="B40" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
+      <c r="V40" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1457,8 +1473,6 @@
       <c r="C41" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
         <v>55</v>
@@ -1477,7 +1491,6 @@
       <c r="D42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
         <v>55</v>
       </c>
@@ -1493,8 +1506,6 @@
       <c r="B43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
@@ -1504,8 +1515,6 @@
       <c r="C44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
         <v>55</v>
@@ -1524,8 +1533,6 @@
       <c r="C45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="L45" s="2" t="s">
         <v>55</v>
@@ -1541,8 +1548,6 @@
       <c r="C46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
         <v>55</v>
@@ -1561,8 +1566,6 @@
       <c r="C47" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="J47" s="2" t="s">
         <v>55</v>
@@ -1581,7 +1584,6 @@
       <c r="F48" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="J48" s="2" t="s">
         <v>55</v>
@@ -1597,7 +1599,6 @@
       <c r="C49" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
         <v>55</v>
       </c>
@@ -1613,8 +1614,6 @@
       <c r="C50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="K50" s="2" t="s">
         <v>55</v>
@@ -1654,8 +1653,6 @@
       <c r="E52" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
         <v>55</v>
@@ -1674,8 +1671,6 @@
       <c r="C53" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
         <v>55</v>
@@ -1808,6 +1803,134 @@
         <v>55</v>
       </c>
       <c r="M61" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>97</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K71" s="2" t="s">
         <v>55</v>
       </c>
     </row>

--- a/People classification.xlsx
+++ b/People classification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/fabio-correa_cordeiro_capgemini_com/Documents/Documents/GitHub/Indigenous-Slavery-KG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBA5C56B-3630-4E9B-A274-43AF753AAFF0}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91445E5B-BEA0-4235-A04F-70989CE44D04}"/>
   <bookViews>
-    <workbookView xWindow="-4620" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
+    <workbookView xWindow="1050" yWindow="-19940" windowWidth="19420" windowHeight="18740" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="100">
   <si>
     <t>tag:stardog:api:deus'</t>
   </si>
@@ -290,45 +290,15 @@
     <t xml:space="preserve"> 'tag:stardog:api:nossa_senhora'</t>
   </si>
   <si>
-    <t>tag:stardog:api:policia</t>
-  </si>
-  <si>
-    <t>tag:stardog:api:ensino_medio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tag:stardog:api:es_sa	</t>
-  </si>
-  <si>
-    <t>tag:stardog:api:seduc</t>
-  </si>
-  <si>
-    <t>tag:stardog:api:tamb_em</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 'tag:stardog:api:candido_rondon'</t>
   </si>
   <si>
     <t xml:space="preserve"> 'tag:stardog:api:nossa_senhora_do_rosario'</t>
   </si>
   <si>
-    <t xml:space="preserve">tag:stardog:api:festa	</t>
-  </si>
-  <si>
-    <t>tag:stardog:api:letras</t>
-  </si>
-  <si>
-    <t>tag:stardog:api:memorias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tag:stardog:api:kariri	</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 'tag:stardog:api:friedrich_nietzsche'</t>
   </si>
   <si>
-    <t>tag:stardog:api:i_sso</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 'tag:stardog:api:bell_hooks'</t>
   </si>
   <si>
@@ -339,6 +309,33 @@
   </si>
   <si>
     <t xml:space="preserve"> 'tag:stardog:api:carolina_maria_de_jesus'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:silvio_romero'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ' tag:stardog:api:orixa'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:sergio_buarque_de_holanda'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:jorge_amado'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:eric_hobsbawm'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:lima_barreto'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:jurgen_habermas'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:d_joao_v'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:joao_pacheco_de_oliveira'</t>
   </si>
 </sst>
 </file>
@@ -741,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093B7361-491F-4850-B66C-DAB516A37F60}">
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
@@ -861,9 +858,7 @@
       <c r="K6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>94</v>
-      </c>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1048,9 +1043,7 @@
       <c r="K17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V17" s="5" t="s">
-        <v>84</v>
-      </c>
+      <c r="V17" s="5"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1069,9 +1062,7 @@
       <c r="K18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V18" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="V18" s="5"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1081,9 +1072,7 @@
         <v>55</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="V19" s="5" t="s">
-        <v>87</v>
-      </c>
+      <c r="V19" s="5"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1099,9 +1088,7 @@
       <c r="L20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V20" s="5" t="s">
-        <v>92</v>
-      </c>
+      <c r="V20" s="5"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1117,6 +1104,7 @@
       <c r="Q21" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="V21" s="5"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1135,6 +1123,7 @@
       <c r="K22" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="V22" s="5"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1156,9 +1145,7 @@
       <c r="K23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V23" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="V23" s="5"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1174,9 +1161,6 @@
       <c r="L24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V24" s="4" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1195,8 +1179,8 @@
       <c r="L25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V25" s="5" t="s">
-        <v>91</v>
+      <c r="V25" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
@@ -1210,8 +1194,8 @@
       <c r="N26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V26" s="5" t="s">
-        <v>93</v>
+      <c r="V26" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -1345,6 +1329,7 @@
       <c r="K33" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="V33" s="5"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -1360,6 +1345,7 @@
       <c r="K34" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="V34" s="5"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -1378,6 +1364,7 @@
       <c r="K35" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="V35" s="5"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -1432,9 +1419,6 @@
       <c r="K38" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V38" s="5" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -1450,9 +1434,7 @@
       <c r="J39" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V39" s="5" t="s">
-        <v>88</v>
-      </c>
+      <c r="V39" s="5"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1462,9 +1444,6 @@
         <v>55</v>
       </c>
       <c r="H40" s="2"/>
-      <c r="V40" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1833,104 +1812,245 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>89</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="C70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>90</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="E71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="C76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>96</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="C78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="D79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>100</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K71" s="2" t="s">
+      <c r="C80" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J80" s="2" t="s">
         <v>55</v>
       </c>
     </row>

--- a/People classification.xlsx
+++ b/People classification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/fabio-correa_cordeiro_capgemini_com/Documents/Documents/GitHub/Indigenous-Slavery-KG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91445E5B-BEA0-4235-A04F-70989CE44D04}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="8_{B14DB1DE-5541-48DD-ABAB-5695742418F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7B0D70-6122-46F0-8653-A64276ECD37E}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-19940" windowWidth="19420" windowHeight="18740" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
+    <workbookView xWindow="-4620" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{60199144-C0FA-4256-8D5B-52EC78D25BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="113">
   <si>
     <t>tag:stardog:api:deus'</t>
   </si>
@@ -200,9 +200,6 @@
     <t>Politico</t>
   </si>
   <si>
-    <t>Escritor</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -336,6 +333,48 @@
   </si>
   <si>
     <t xml:space="preserve"> 'tag:stardog:api:joao_pacheco_de_oliveira'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:jose_murilo_de_carvalho'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:euclides_da_cunha'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:walter_benjamin'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:angela_davis'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:nilma_lino_gomes'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:martin_heidegger'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:tashka_yawanawa'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:jose_do_patrocinio'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:dilma_rousseff'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:sueli_maxakali'</t>
+  </si>
+  <si>
+    <t>Escritor / Artista</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:toninho_maxakali'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:castro_alves'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'tag:stardog:api:benjamin_constant'</t>
   </si>
 </sst>
 </file>
@@ -738,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093B7361-491F-4850-B66C-DAB516A37F60}">
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" customWidth="1"/>
@@ -763,40 +802,40 @@
         <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -804,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H3" s="2"/>
     </row>
@@ -813,17 +852,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -831,17 +870,17 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -849,14 +888,14 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V6" s="5"/>
     </row>
@@ -865,7 +904,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7" s="2"/>
       <c r="V7" s="5"/>
@@ -875,14 +914,14 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -890,14 +929,14 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="2"/>
       <c r="P9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -905,17 +944,17 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -923,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -932,17 +971,17 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -950,14 +989,14 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -965,20 +1004,20 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -986,26 +1025,26 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -1013,17 +1052,17 @@
         <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
@@ -1031,17 +1070,17 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V17" s="5"/>
     </row>
@@ -1050,17 +1089,17 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V18" s="5"/>
     </row>
@@ -1069,7 +1108,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19" s="2"/>
       <c r="V19" s="5"/>
@@ -1079,14 +1118,14 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V20" s="5"/>
     </row>
@@ -1095,14 +1134,14 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V21" s="5"/>
     </row>
@@ -1111,17 +1150,17 @@
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V22" s="5"/>
     </row>
@@ -1130,20 +1169,20 @@
         <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V23" s="5"/>
     </row>
@@ -1152,14 +1191,14 @@
         <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
@@ -1167,20 +1206,20 @@
         <v>22</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
@@ -1188,14 +1227,14 @@
         <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
@@ -1203,14 +1242,14 @@
         <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V27" s="5"/>
     </row>
@@ -1219,14 +1258,14 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V28" s="5"/>
     </row>
@@ -1235,14 +1274,14 @@
         <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H29" s="2"/>
       <c r="L29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V29" s="5"/>
     </row>
@@ -1251,26 +1290,26 @@
         <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V30" s="5"/>
     </row>
@@ -1279,7 +1318,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H31" s="2"/>
       <c r="V31" s="5"/>
@@ -1289,20 +1328,20 @@
         <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V32" s="5"/>
     </row>
@@ -1311,23 +1350,23 @@
         <v>30</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V33" s="5"/>
     </row>
@@ -1336,14 +1375,14 @@
         <v>31</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V34" s="5"/>
     </row>
@@ -1352,17 +1391,17 @@
         <v>32</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V35" s="5"/>
     </row>
@@ -1371,14 +1410,14 @@
         <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H36" s="2"/>
       <c r="L36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
@@ -1386,20 +1425,20 @@
         <v>34</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
@@ -1407,17 +1446,17 @@
         <v>35</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
@@ -1425,14 +1464,14 @@
         <v>36</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V39" s="5"/>
     </row>
@@ -1441,7 +1480,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H40" s="2"/>
     </row>
@@ -1450,17 +1489,17 @@
         <v>38</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
@@ -1468,14 +1507,14 @@
         <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H42" s="2"/>
       <c r="L42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
@@ -1483,7 +1522,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H43" s="2"/>
     </row>
@@ -1492,17 +1531,17 @@
         <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
@@ -1510,14 +1549,14 @@
         <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H45" s="2"/>
       <c r="L45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
@@ -1525,17 +1564,17 @@
         <v>43</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
@@ -1543,14 +1582,14 @@
         <v>44</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H47" s="2"/>
       <c r="J47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
@@ -1558,17 +1597,17 @@
         <v>45</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H48" s="2"/>
       <c r="J48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
@@ -1576,14 +1615,14 @@
         <v>46</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
@@ -1591,14 +1630,14 @@
         <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -1606,20 +1645,20 @@
         <v>48</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H51" s="2"/>
       <c r="L51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
@@ -1627,20 +1666,20 @@
         <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -1648,396 +1687,405 @@
         <v>50</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>55</v>
+      <c r="D68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>88</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M69" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>55</v>
+      <c r="C69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>89</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>55</v>
+      <c r="E70" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>90</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>55</v>
+        <v>91</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>55</v>
+        <v>90</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>94</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>55</v>
+      <c r="C75" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>95</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>55</v>
+      <c r="E76" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>96</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>55</v>
+      <c r="C77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>97</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>55</v>
+      <c r="D78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>98</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N79" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>55</v>
+      <c r="C79" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
@@ -2045,13 +2093,226 @@
         <v>99</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>100</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
